--- a/data/trans_dic/P56$familiarvive-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiarvive-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,56; 64,96</t>
+          <t>14,45; 64,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,91; 43,96</t>
+          <t>8,57; 44,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 15,8</t>
+          <t>1,79; 14,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,33; 79,32</t>
+          <t>28,36; 79,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 30,36</t>
+          <t>7,41; 29,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,03; 25,78</t>
+          <t>2,99; 25,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,72; 28,23</t>
+          <t>14,49; 27,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,01; 64,41</t>
+          <t>28,01; 64,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,75; 23,84</t>
+          <t>5,78; 25,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 26,93</t>
+          <t>7,55; 26,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,81; 22,58</t>
+          <t>11,75; 22,19</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,09</t>
+          <t>0,0; 34,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 32,6</t>
+          <t>6,18; 32,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,02; 30,81</t>
+          <t>3,96; 33,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 24,6</t>
+          <t>4,0; 25,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,21; 62,8</t>
+          <t>22,14; 63,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,74; 39,99</t>
+          <t>17,84; 41,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,69; 59,34</t>
+          <t>23,76; 56,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,34; 29,76</t>
+          <t>15,02; 29,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,82; 45,06</t>
+          <t>17,38; 46,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,93; 33,75</t>
+          <t>15,66; 34,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,05; 45,05</t>
+          <t>19,18; 45,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,33; 24,84</t>
+          <t>13,81; 25,66</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,16</t>
+          <t>0,0; 66,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,94</t>
+          <t>0,0; 61,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,99; 47,95</t>
+          <t>8,83; 47,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,53; 45,79</t>
+          <t>10,4; 46,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,39; 70,08</t>
+          <t>20,89; 68,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,33; 56,61</t>
+          <t>23,98; 55,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,5; 59,69</t>
+          <t>24,44; 60,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,81; 37,06</t>
+          <t>16,41; 36,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,18; 61,11</t>
+          <t>22,0; 59,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22,97; 50,85</t>
+          <t>21,64; 50,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22,48; 52,94</t>
+          <t>21,69; 52,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,21; 34,72</t>
+          <t>17,0; 35,42</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,55</t>
+          <t>0,0; 31,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,23; 59,87</t>
+          <t>13,92; 63,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,71</t>
+          <t>0,0; 29,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 23,71</t>
+          <t>5,15; 25,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,22; 50,03</t>
+          <t>16,96; 52,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,51; 44,76</t>
+          <t>19,05; 44,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,15; 33,3</t>
+          <t>9,47; 34,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,28; 28,32</t>
+          <t>14,84; 28,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,09; 40,85</t>
+          <t>13,34; 41,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,7; 42,88</t>
+          <t>20,34; 43,62</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,71; 29,33</t>
+          <t>7,73; 27,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,81; 23,63</t>
+          <t>12,46; 22,89</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,93; 31,83</t>
+          <t>9,98; 31,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,0; 32,85</t>
+          <t>11,3; 32,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,08; 27,03</t>
+          <t>9,8; 25,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,79; 19,05</t>
+          <t>8,69; 19,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,8; 51,58</t>
+          <t>30,49; 51,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,88; 34,68</t>
+          <t>22,53; 35,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,26; 34,14</t>
+          <t>19,54; 34,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,19; 25,71</t>
+          <t>18,03; 25,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,87; 41,88</t>
+          <t>26,57; 41,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,36; 31,59</t>
+          <t>20,46; 31,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,0; 29,82</t>
+          <t>18,4; 29,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,2; 22,32</t>
+          <t>16,43; 22,21</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1906; 8503</t>
+          <t>1891; 8378</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1808</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1690; 8340</t>
+          <t>1627; 8374</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>441; 3964</t>
+          <t>448; 3566</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4643; 12999</t>
+          <t>4648; 13082</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3290; 14002</t>
+          <t>3415; 13429</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1206; 10267</t>
+          <t>1192; 10259</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9101; 17459</t>
+          <t>8962; 16921</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8552; 18988</t>
+          <t>8256; 19080</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3261; 13519</t>
+          <t>3278; 14306</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4369; 15835</t>
+          <t>4438; 15626</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10267; 19630</t>
+          <t>10217; 19289</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4654</t>
+          <t>0; 5146</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2052; 10563</t>
+          <t>2003; 10499</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>784; 6008</t>
+          <t>772; 6579</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>800; 6008</t>
+          <t>977; 6255</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6352; 17187</t>
+          <t>6060; 17427</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10994; 26257</t>
+          <t>11717; 27015</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9727; 24369</t>
+          <t>9757; 23314</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9598; 19914</t>
+          <t>10052; 19619</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6276; 19079</t>
+          <t>7360; 19683</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15616; 33092</t>
+          <t>15355; 33589</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11537; 27286</t>
+          <t>11616; 27418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12173; 22685</t>
+          <t>12610; 23441</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4671</t>
+          <t>0; 4626</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 9215</t>
+          <t>0; 8628</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1580; 8430</t>
+          <t>1552; 8430</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2138; 9293</t>
+          <t>2110; 9377</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3597; 12367</t>
+          <t>3686; 12132</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10268; 23886</t>
+          <t>10117; 23468</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8235; 20919</t>
+          <t>8566; 21209</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6677; 15650</t>
+          <t>6931; 15389</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5457; 15033</t>
+          <t>5413; 14705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12900; 28566</t>
+          <t>12156; 28265</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11830; 27861</t>
+          <t>11413; 27678</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10758; 21708</t>
+          <t>10629; 22145</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4981</t>
+          <t>0; 4185</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3066; 12899</t>
+          <t>2999; 13681</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3324</t>
+          <t>0; 4796</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1726; 7646</t>
+          <t>1660; 8143</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5535; 16081</t>
+          <t>5452; 16783</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9492; 22949</t>
+          <t>9768; 22659</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5110; 18600</t>
+          <t>5290; 19242</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11433; 22672</t>
+          <t>11879; 23137</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6398; 18550</t>
+          <t>6059; 18840</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15072; 31227</t>
+          <t>14813; 31761</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5543; 21088</t>
+          <t>5560; 19831</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14383; 26540</t>
+          <t>13995; 25700</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4792; 15366</t>
+          <t>4817; 15129</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9419; 25791</t>
+          <t>8874; 25277</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7267; 19490</t>
+          <t>7062; 18504</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8975; 19445</t>
+          <t>8866; 20107</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28816; 48252</t>
+          <t>28525; 48161</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44914; 71179</t>
+          <t>46249; 73395</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33081; 58651</t>
+          <t>33564; 59659</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>45665; 64538</t>
+          <t>45255; 64689</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36686; 59390</t>
+          <t>37688; 59486</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>57759; 89642</t>
+          <t>58046; 88452</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43897; 72721</t>
+          <t>44872; 73135</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>57186; 78795</t>
+          <t>57999; 78421</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$familiarvive-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiarvive-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,45; 64,0</t>
+          <t>14,3; 64,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,52 +727,52 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,57; 44,14</t>
+          <t>8,34; 43,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 14,21</t>
+          <t>1,66; 14,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,36; 79,83</t>
+          <t>27,59; 76,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,41; 29,12</t>
+          <t>7,08; 30,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 25,76</t>
+          <t>3,01; 26,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,49; 27,36</t>
+          <t>14,64; 28,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,01; 64,72</t>
+          <t>28,87; 63,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,78; 25,23</t>
+          <t>5,78; 23,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 26,58</t>
+          <t>7,79; 27,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,75; 22,19</t>
+          <t>11,79; 22,75</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,38</t>
+          <t>0,0; 30,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>6,18; 32,41</t>
+          <t>5,92; 34,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 33,74</t>
+          <t>3,96; 33,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 25,61</t>
+          <t>4,36; 26,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,14; 63,67</t>
+          <t>22,15; 62,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,84; 41,14</t>
+          <t>17,75; 40,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,76; 56,77</t>
+          <t>22,94; 57,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,02; 29,32</t>
+          <t>14,53; 29,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17,38; 46,49</t>
+          <t>15,7; 47,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,66; 34,25</t>
+          <t>15,92; 34,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,18; 45,27</t>
+          <t>18,48; 43,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,81; 25,66</t>
+          <t>13,41; 25,58</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,51</t>
+          <t>0,0; 67,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,74</t>
+          <t>0,0; 65,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,83; 47,95</t>
+          <t>9,2; 50,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,4; 46,2</t>
+          <t>10,96; 43,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,89; 68,75</t>
+          <t>20,23; 68,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,98; 55,62</t>
+          <t>24,55; 54,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,44; 60,52</t>
+          <t>23,74; 61,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,41; 36,45</t>
+          <t>16,18; 37,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,0; 59,78</t>
+          <t>21,9; 61,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,64; 50,32</t>
+          <t>20,62; 47,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,69; 52,59</t>
+          <t>22,5; 51,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,0; 35,42</t>
+          <t>16,15; 34,42</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,54</t>
+          <t>0,0; 37,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,92; 63,5</t>
+          <t>14,36; 60,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,89</t>
+          <t>0,0; 20,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 25,26</t>
+          <t>4,65; 23,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,96; 52,22</t>
+          <t>17,15; 49,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,05; 44,19</t>
+          <t>18,26; 43,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,47; 34,45</t>
+          <t>9,59; 34,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,84; 28,9</t>
+          <t>14,28; 27,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,34; 41,49</t>
+          <t>14,63; 39,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,34; 43,62</t>
+          <t>20,55; 42,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,73; 27,58</t>
+          <t>8,23; 27,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,46; 22,89</t>
+          <t>13,0; 23,56</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,98; 31,33</t>
+          <t>9,48; 31,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,3; 32,2</t>
+          <t>10,89; 31,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,8; 25,67</t>
+          <t>9,32; 25,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,69; 19,7</t>
+          <t>8,63; 19,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,49; 51,48</t>
+          <t>30,27; 51,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,53; 35,76</t>
+          <t>22,16; 35,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,54; 34,73</t>
+          <t>19,62; 34,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>18,03; 25,77</t>
+          <t>17,97; 25,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26,57; 41,94</t>
+          <t>26,23; 41,11</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,46; 31,17</t>
+          <t>19,94; 31,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,4; 29,99</t>
+          <t>18,57; 29,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,43; 22,21</t>
+          <t>16,14; 22,32</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14391</t>
+          <t>15302</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1891; 8378</t>
+          <t>1872; 8458</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1655,52 +1655,52 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1627; 8374</t>
+          <t>1582; 8214</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>448; 3566</t>
+          <t>433; 3727</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4648; 13082</t>
+          <t>4521; 12513</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3415; 13429</t>
+          <t>3265; 14287</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1192; 10259</t>
+          <t>1200; 10374</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8962; 16921</t>
+          <t>9633; 18769</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8256; 19080</t>
+          <t>8510; 18697</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3278; 14306</t>
+          <t>3277; 13288</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4438; 15626</t>
+          <t>4578; 15914</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10217; 19289</t>
+          <t>10832; 20900</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14315</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>19086</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5146</t>
+          <t>0; 4574</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2003; 10499</t>
+          <t>1917; 11138</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>772; 6579</t>
+          <t>773; 6604</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>977; 6255</t>
+          <t>1146; 7039</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6060; 17427</t>
+          <t>6061; 17121</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11717; 27015</t>
+          <t>11654; 26492</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9757; 23314</t>
+          <t>9422; 23611</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10052; 19619</t>
+          <t>10756; 21986</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7360; 19683</t>
+          <t>6646; 20030</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15355; 33589</t>
+          <t>15608; 33701</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11616; 27418</t>
+          <t>11189; 26179</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12610; 23441</t>
+          <t>13445; 25651</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10661</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15946</t>
+          <t>17546</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4626</t>
+          <t>0; 4698</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 8628</t>
+          <t>0; 9111</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1552; 8430</t>
+          <t>1617; 8853</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2110; 9377</t>
+          <t>2534; 10169</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3686; 12132</t>
+          <t>3569; 12148</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10117; 23468</t>
+          <t>10359; 23117</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8566; 21209</t>
+          <t>8321; 21452</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6931; 15389</t>
+          <t>7718; 17707</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5413; 14705</t>
+          <t>5389; 15194</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12156; 28265</t>
+          <t>11583; 26909</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11413; 27678</t>
+          <t>11843; 26922</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10629; 22145</t>
+          <t>11435; 24376</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16297</t>
+          <t>17759</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20008</t>
+          <t>21683</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4185</t>
+          <t>0; 4993</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2999; 13681</t>
+          <t>3094; 12933</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4796</t>
+          <t>0; 3253</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1660; 8143</t>
+          <t>1540; 7855</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5452; 16783</t>
+          <t>5512; 15934</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9768; 22659</t>
+          <t>9360; 22163</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5290; 19242</t>
+          <t>5357; 19116</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11879; 23137</t>
+          <t>12552; 24103</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6059; 18840</t>
+          <t>6643; 17979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14813; 31761</t>
+          <t>14962; 31193</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5560; 19831</t>
+          <t>5919; 19992</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13995; 25700</t>
+          <t>15727; 28512</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>14260</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>54228</t>
+          <t>59356</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>67497</t>
+          <t>73617</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4817; 15129</t>
+          <t>4577; 15035</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8874; 25277</t>
+          <t>8549; 24337</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7062; 18504</t>
+          <t>6720; 18714</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8866; 20107</t>
+          <t>9375; 21685</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28525; 48161</t>
+          <t>28318; 48416</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46249; 73395</t>
+          <t>45488; 72089</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33564; 59659</t>
+          <t>33698; 59433</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>45255; 64689</t>
+          <t>49485; 70898</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37688; 59486</t>
+          <t>37203; 58298</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58046; 88452</t>
+          <t>56592; 89886</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44872; 73135</t>
+          <t>45284; 73120</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>57999; 78421</t>
+          <t>61989; 85717</t>
         </is>
       </c>
     </row>
